--- a/Restoration Mountaine Forest - Full Seedling Plantation NTFP (Agroforestry).xlsx
+++ b/Restoration Mountaine Forest - Full Seedling Plantation NTFP (Agroforestry).xlsx
@@ -5073,7 +5073,7 @@
         <v>Coffea arabica</v>
       </c>
       <c r="FL7">
-        <v>80</v>
+        <v>4.64</v>
       </c>
       <c r="FM7">
         <v>1</v>
